--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/GIR Somnath.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/GIR Somnath.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94F94286-4BD0-4F18-BBEF-4F388A70CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E59369C-7B07-4C47-BF2F-63025624829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -37,13 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
-  <si>
-    <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Name of crop,   No. of exp.  And Order of selection                                                          Season: Kharif  </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="44">
   <si>
     <t>PART- A</t>
   </si>
@@ -81,9 +75,6 @@
     <t>Total Part- A + B</t>
   </si>
   <si>
-    <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                 state                                                                                   </t>
-  </si>
-  <si>
     <t>Year-2026-27</t>
   </si>
   <si>
@@ -151,13 +142,40 @@
   </si>
   <si>
     <t>UNA-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                 GUJARAT                                              STATEMENT NO. 4                                                 STATE                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">             Name of crop,          No. of exp.    And      Order of selection                                         Season: Kharif  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                          GUJARAT                                              STATEMENT NO. 4                      CENTRAL                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Name of crop,   No. of exp.  And Order of selection                                           Season: Kharif  </t>
+  </si>
+  <si>
+    <t>NOTE:  NO PLANNING OF BAJRA IN GIR SOMNATH SO BAJRA(4) PLANNING TRANSFERED TO AMRELI</t>
+  </si>
+  <si>
+    <t>BAJRA</t>
+  </si>
+  <si>
+    <t>14-4=10</t>
+  </si>
+  <si>
+    <t>20-4=16</t>
+  </si>
+  <si>
+    <t>NO PLANNING</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,6 +194,20 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -208,7 +240,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -340,24 +372,27 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color theme="0"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -371,6 +406,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -380,37 +474,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -430,6 +500,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,306 +802,363 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="1" max="3" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="7.5546875" customWidth="1"/>
+    <col min="6" max="8" width="9.44140625" customWidth="1"/>
+    <col min="9" max="9" width="7.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="33"/>
+      <c r="C4" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="29">
+        <v>10</v>
+      </c>
+      <c r="E4" s="29"/>
+      <c r="F4" s="18">
+        <v>4</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="29">
+        <v>6</v>
+      </c>
+      <c r="I4" s="29"/>
+      <c r="J4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="25" t="s">
+    </row>
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="30"/>
+      <c r="J5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="8">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="9">
+        <f>+D7+H7</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5">
+        <v>4</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="9">
+        <f t="shared" ref="J8:J12" si="0">+D8+H8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="17">
-        <v>10</v>
-      </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17">
-        <v>6</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="19" t="s">
+      <c r="B9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="1">
-        <f>+D4+F4</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2</v>
-      </c>
-      <c r="E7" s="8">
-        <v>5</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="3">
-        <f>+D7+F7</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="9">
-        <v>2</v>
-      </c>
-      <c r="E8" s="8">
-        <v>4</v>
-      </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="3">
-        <f t="shared" ref="H8:H12" si="0">+D8+F8</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="8">
-        <v>2</v>
-      </c>
-      <c r="F9" s="9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="D9" s="8">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="8">
+        <v>2</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="8">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>3</v>
+      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="8">
+        <v>2</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9">
-        <v>2</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="9">
-        <v>2</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="D12" s="8">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
         <v>1</v>
       </c>
-      <c r="F12" s="9">
-        <v>2</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="8">
+        <v>2</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="4">
         <f>SUM(D7:D12)</f>
         <v>10</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4">
-        <f>SUM(F7:F12)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4">
         <f>SUM(H7:H12)</f>
+        <v>6</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4">
+        <f>SUM(J7:J12)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-    </row>
-    <row r="15" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="28"/>
       <c r="D16" s="4">
-        <v>0</v>
+        <f>+D13+D15</f>
+        <v>10</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4">
@@ -1018,359 +1166,414 @@
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="4">
-        <f>+D13+D16</f>
-        <v>10</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4">
-        <f>+F13+F16</f>
+        <f>+H13+H15</f>
         <v>6</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4">
-        <f>+H13+H16</f>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4">
+        <f>+J13+J15</f>
         <v>16</v>
       </c>
     </row>
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F7:G12"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" customWidth="1"/>
+    <col min="4" max="9" width="9.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-    </row>
-    <row r="2" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="18">
+        <v>6</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
+        <v>4</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
+        <v>4</v>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="17">
-        <v>6</v>
-      </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17">
-        <v>6</v>
-      </c>
-      <c r="G4" s="17"/>
-      <c r="H4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
       <c r="D5" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E5" s="19"/>
       <c r="F5" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="1">
-        <f>+D4+F4</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="13"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="14">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="40"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="13"/>
+    </row>
+    <row r="9" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="14">
+        <v>2</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="14">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="14">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="9">
-        <v>2</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1</v>
-      </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="3">
-        <f>+D7+F7</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="9">
-        <v>2</v>
-      </c>
-      <c r="E8" s="10">
-        <v>3</v>
-      </c>
-      <c r="F8" s="9">
-        <v>2</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="3">
-        <f t="shared" ref="H8:H11" si="0">+D8+F8</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="9">
-        <v>2</v>
-      </c>
-      <c r="E10" s="10">
-        <v>2</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9">
-        <v>2</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="4">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="7">
         <f>SUM(D7:D11)</f>
         <v>6</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4">
-        <f>SUM(F7:F11)</f>
-        <v>6</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7">
         <f>SUM(H7:H11)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+    </row>
+    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A15" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="4">
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="7">
         <f>+D12+D14</f>
         <v>6</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4">
-        <f>+F12+F14</f>
-        <v>6</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7">
         <f>+H12+H14</f>
-        <v>12</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7">
+        <f>+J12+J14</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
+  <mergeCells count="17">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A16:J16"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F7:G11"/>
+    <mergeCell ref="A13:J13"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
     <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>